--- a/project/sample-imports/patients-uat2.xlsx
+++ b/project/sample-imports/patients-uat2.xlsx
@@ -46,7 +46,7 @@
     <t>Mthembu</t>
   </si>
   <si>
-    <t>makabmahlalela+uat2patient1@gmail.com</t>
+    <t>aymish143+uat2patient1@gmail.com</t>
   </si>
   <si>
     <t>8803141345081</t>
@@ -70,7 +70,7 @@
     <t>Ngcobo</t>
   </si>
   <si>
-    <t>maziyamayo7+uat2patient2@gmail.com</t>
+    <t>aymish143+uat2patient2@gmail.com</t>
   </si>
   <si>
     <t>7911025345084</t>
@@ -94,7 +94,7 @@
     <t>Sithole</t>
   </si>
   <si>
-    <t>makabmahlalela+uat2patient3@gmail.com</t>
+    <t>aymish143+uat2patient3@gmail.com</t>
   </si>
   <si>
     <t>9507212345081</t>
@@ -115,7 +115,7 @@
     <t>Botha</t>
   </si>
   <si>
-    <t>maziyamayo7+uat2patient4@gmail.com</t>
+    <t>aymish143+uat2patient4@gmail.com</t>
   </si>
   <si>
     <t>6801306345088</t>
@@ -136,7 +136,7 @@
     <t>Mahlangu</t>
   </si>
   <si>
-    <t>makabmahlalela+uat2patient5@gmail.com</t>
+    <t>aymish143+uat2patient5@gmail.com</t>
   </si>
   <si>
     <t>0109093345089</t>
@@ -683,6 +683,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>